--- a/template/los.xlsx
+++ b/template/los.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teleprimeadmin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp\www\sv\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8498B4B-D373-40C6-95E5-913C2E6744AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325BBFCC-B91F-4C0D-BA82-07AC87C852BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{412596C9-7146-4243-98CC-82EBABAD17CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{412596C9-7146-4243-98CC-82EBABAD17CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,187 +34,229 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t>CUSTOMER NO</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>2ND CARD TYPE/CL</t>
-  </si>
-  <si>
-    <t>SOURCE CODE</t>
-  </si>
-  <si>
-    <t>PREFERRED PRODUCT CODE</t>
-  </si>
-  <si>
-    <t>NAME OF APPLICANT</t>
-  </si>
-  <si>
-    <t>TITLE</t>
-  </si>
-  <si>
-    <t>LASTNAME</t>
-  </si>
-  <si>
-    <t>FIRSTNAME</t>
-  </si>
-  <si>
-    <t>MIDDLENAME</t>
-  </si>
-  <si>
-    <t>NAME ON FILE</t>
-  </si>
-  <si>
-    <t>NAME TO APPEAR ON THE CARD</t>
-  </si>
-  <si>
-    <t>NATIONALITY</t>
-  </si>
-  <si>
-    <t>IF US CITIZEN (US TIN )</t>
-  </si>
-  <si>
-    <t>MOBILE NUMBER ON FILE</t>
-  </si>
-  <si>
-    <t>LANDLINE NUMBER ON FILE</t>
-  </si>
-  <si>
-    <t>SSS (AS PER TM)</t>
-  </si>
-  <si>
-    <t>TIN (AS PER RBSC FILE)</t>
-  </si>
-  <si>
-    <t>TIN (AS PER TM)</t>
-  </si>
-  <si>
-    <t>EMAIL ADDRESS</t>
-  </si>
-  <si>
-    <t>E-SOA</t>
-  </si>
-  <si>
-    <t>WEB SHOPPER</t>
-  </si>
-  <si>
-    <t>HAVE YOU STAYED IN THE USA FOR 180 DAYS IN THE LAST 3 YRS (YES/NO)</t>
-  </si>
-  <si>
-    <t>CUSTOMER PROFILE (FATCA)</t>
-  </si>
-  <si>
-    <t>DECLARED INCOME</t>
-  </si>
-  <si>
-    <t>BILLING ADDRESS CHANNEL</t>
-  </si>
-  <si>
-    <t>CARD DELIVERY CHANNEL</t>
-  </si>
-  <si>
-    <t>PAYMENT MODE</t>
-  </si>
-  <si>
-    <t>DOCUMENT TYPE PRESENTED</t>
-  </si>
-  <si>
-    <t>PRESENT ADDRESS 1</t>
-  </si>
-  <si>
-    <t>PRESENT ADDRESS 2</t>
-  </si>
-  <si>
-    <t>PRESENT ADDRESS 3</t>
-  </si>
-  <si>
-    <t>PRESENT ADDRESS 4</t>
-  </si>
-  <si>
-    <t>PRESENT COUNTRY CODE</t>
-  </si>
-  <si>
-    <t>PRESENT PROVINCE</t>
-  </si>
-  <si>
-    <t>PRESENT CITY</t>
-  </si>
-  <si>
-    <t>PRESENT ZIP CODE</t>
-  </si>
-  <si>
-    <t>PERMANENT ADDRESS 1</t>
-  </si>
-  <si>
-    <t>PERMANENT ADDRESS 2</t>
-  </si>
-  <si>
-    <t>PERMANENT ADDRESS 3</t>
-  </si>
-  <si>
-    <t>PERMANENT ADDRESS 4</t>
-  </si>
-  <si>
-    <t>PERMANENT COUNTRY CODE</t>
-  </si>
-  <si>
-    <t>PERMANENT PROVINCE</t>
-  </si>
-  <si>
-    <t>PERMANENT CITY</t>
-  </si>
-  <si>
-    <t>PERMANENT ZIP CODE</t>
-  </si>
-  <si>
-    <t>EMPLOYERS NAME</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT ADDRESS 1</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT ADDRESS 2</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT ADDRESS 3</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT ADDRESS 4</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT COUNTRY CODE</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT PROVINCE</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT  CITY</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT  ZIP CODE</t>
-  </si>
-  <si>
-    <t>WITH PERSONAL INFORMATION CHANGE</t>
-  </si>
-  <si>
-    <t>On Authority to Disclose:(YES/NO)</t>
-  </si>
-  <si>
-    <t>REMARKS</t>
-  </si>
-  <si>
-    <t>AGREED TO E-SOA FOR THEIR 1ST CARD</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>middle_name</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>gender_code</t>
+  </si>
+  <si>
+    <t>marital_status_description</t>
+  </si>
+  <si>
+    <t>nationality_desc</t>
+  </si>
+  <si>
+    <t>place_of_birth</t>
+  </si>
+  <si>
+    <t>mobile_number</t>
+  </si>
+  <si>
+    <t>address_line1</t>
+  </si>
+  <si>
+    <t>address_line2</t>
+  </si>
+  <si>
+    <t>address_line3</t>
+  </si>
+  <si>
+    <t>address_line4</t>
+  </si>
+  <si>
+    <t>zip_code</t>
+  </si>
+  <si>
+    <t>fund_source_desc</t>
+  </si>
+  <si>
+    <t>occupation_desc</t>
+  </si>
+  <si>
+    <t>industry_desc</t>
+  </si>
+  <si>
+    <t>name_of_employer</t>
+  </si>
+  <si>
+    <t>business_address1</t>
+  </si>
+  <si>
+    <t>business_address2</t>
+  </si>
+  <si>
+    <t>business_address3</t>
+  </si>
+  <si>
+    <t>business_city</t>
+  </si>
+  <si>
+    <t>business_province</t>
+  </si>
+  <si>
+    <t>business_country</t>
+  </si>
+  <si>
+    <t>business_zip_code</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>sss</t>
+  </si>
+  <si>
+    <t>employment_type</t>
+  </si>
+  <si>
+    <t>cust_no</t>
+  </si>
+  <si>
+    <t>act_no</t>
+  </si>
+  <si>
+    <t>curr_adb</t>
+  </si>
+  <si>
+    <t>mtadb_3m</t>
+  </si>
+  <si>
+    <t>mtadb_6m</t>
+  </si>
+  <si>
+    <t>avg_paycredit</t>
+  </si>
+  <si>
+    <t>old_branch_name</t>
+  </si>
+  <si>
+    <t>branch_cd</t>
+  </si>
+  <si>
+    <t>complete_tag</t>
+  </si>
+  <si>
+    <t>payroll_tag</t>
+  </si>
+  <si>
+    <t>pm_address1</t>
+  </si>
+  <si>
+    <t>pm_address2</t>
+  </si>
+  <si>
+    <t>pm_address3</t>
+  </si>
+  <si>
+    <t>pm_address4</t>
+  </si>
+  <si>
+    <t>pm_zipcode</t>
+  </si>
+  <si>
+    <t>annual_income</t>
+  </si>
+  <si>
+    <t>phone_number</t>
+  </si>
+  <si>
+    <t>email_address</t>
+  </si>
+  <si>
+    <t>phone_off</t>
+  </si>
+  <si>
+    <t>dtd_open</t>
+  </si>
+  <si>
+    <t>acct_type</t>
+  </si>
+  <si>
+    <t>source_code</t>
+  </si>
+  <si>
+    <t>card_type</t>
+  </si>
+  <si>
+    <t>card_product</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>visa_id</t>
+  </si>
+  <si>
+    <t>id_type</t>
+  </si>
+  <si>
+    <t>HC_tag</t>
+  </si>
+  <si>
+    <t>SEGMENT</t>
+  </si>
+  <si>
+    <t>Date_of_Tagging</t>
+  </si>
+  <si>
+    <t>Tagging_Year</t>
+  </si>
+  <si>
+    <t>Tagging_Month</t>
+  </si>
+  <si>
+    <t>SOL_ID</t>
+  </si>
+  <si>
+    <t>identification_no</t>
+  </si>
+  <si>
+    <t>CL_Assignment</t>
+  </si>
+  <si>
+    <t>Existing_World_MC</t>
+  </si>
+  <si>
+    <t>Existing_HC_Privilege</t>
+  </si>
+  <si>
+    <t>position_code</t>
+  </si>
+  <si>
+    <t>last_maintenance_date</t>
+  </si>
+  <si>
+    <t>first_imported_date</t>
+  </si>
+  <si>
+    <t>preferred_product_code</t>
+  </si>
+  <si>
+    <t>name_appear_on_the_card</t>
+  </si>
+  <si>
+    <t>remarks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,59 +265,65 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -285,29 +333,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -315,55 +350,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,149 +700,151 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DAAC343-7E81-4CC6-8E89-0FAAC2BC1ACA}">
-  <dimension ref="A1:BF2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CD2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.140625" customWidth="1"/>
-    <col min="12" max="12" width="37.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.109375" customWidth="1"/>
+    <col min="12" max="12" width="37.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="41" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="50" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="41" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="50" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="28" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="54.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="54.88671875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="23.21875" customWidth="1"/>
+    <col min="72" max="72" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:82" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
@@ -833,141 +856,217 @@
       <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="5" t="s">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="11" t="s">
+      <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="4"/>
     </row>
-    <row r="2" spans="1:58" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="7"/>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="7"/>
-      <c r="AI2" s="7"/>
-      <c r="AJ2" s="7"/>
-      <c r="AK2" s="7"/>
-      <c r="AL2" s="7"/>
-      <c r="AM2" s="7"/>
-      <c r="AN2" s="7"/>
-      <c r="AO2" s="7"/>
-      <c r="AP2" s="7"/>
-      <c r="AQ2" s="7"/>
-      <c r="AR2" s="7"/>
-      <c r="AS2" s="7"/>
-      <c r="AT2" s="7"/>
-      <c r="AU2" s="7"/>
-      <c r="AV2" s="7"/>
-      <c r="AW2" s="7"/>
-      <c r="AX2" s="7"/>
-      <c r="AY2" s="7"/>
-      <c r="AZ2" s="7"/>
-      <c r="BA2" s="7"/>
-      <c r="BB2" s="7"/>
-      <c r="BC2" s="7"/>
-      <c r="BD2" s="7"/>
-      <c r="BE2" s="15"/>
-      <c r="BF2" s="7"/>
+    <row r="2" spans="1:82" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="10"/>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="6"/>
+      <c r="BG2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="6"/>
+      <c r="BJ2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="6"/>
+      <c r="BT2" s="11"/>
+      <c r="BU2" s="12"/>
+      <c r="BV2" s="12"/>
+      <c r="BW2" s="12"/>
+      <c r="BX2" s="12"/>
+      <c r="BY2" s="12"/>
+      <c r="BZ2" s="12"/>
+      <c r="CA2" s="12"/>
+      <c r="CB2" s="12"/>
+      <c r="CC2" s="12"/>
+      <c r="CD2" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
